--- a/data/trans_dic/P55$privada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,29; 16,81</t>
+          <t>5,92; 17,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 20,01</t>
+          <t>6,89; 19,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,27; 21,82</t>
+          <t>8,7; 22,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 20,68</t>
+          <t>9,32; 20,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 22,71</t>
+          <t>11,9; 22,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,01</t>
+          <t>10,64; 19,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 19,81</t>
+          <t>8,66; 19,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 20,03</t>
+          <t>13,08; 19,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 19,15</t>
+          <t>10,98; 18,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 17,98</t>
+          <t>10,2; 17,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,02; 18,66</t>
+          <t>10,32; 18,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 18,85</t>
+          <t>12,94; 18,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,23</t>
+          <t>0,0; 25,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 44,43</t>
+          <t>5,11; 45,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 35,85</t>
+          <t>6,74; 36,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 28,14</t>
+          <t>9,16; 27,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,52; 84,76</t>
+          <t>30,22; 84,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 56,81</t>
+          <t>13,29; 55,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 29,22</t>
+          <t>7,63; 33,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,19; 32,12</t>
+          <t>16,22; 33,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,48; 51,68</t>
+          <t>13,61; 52,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 42,57</t>
+          <t>11,56; 42,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 27,95</t>
+          <t>8,82; 28,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,17; 26,78</t>
+          <t>14,49; 27,03</t>
         </is>
       </c>
     </row>
@@ -997,27 +997,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,46; 79,71</t>
+          <t>8,9; 73,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,07; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,76; 49,05</t>
+          <t>11,49; 48,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,04; 84,52</t>
+          <t>33,92; 91,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,91; 50,24</t>
+          <t>15,81; 52,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,29; 76,82</t>
+          <t>28,52; 74,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 100,0</t>
+          <t>16,91; 100,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 84,28</t>
+          <t>10,77; 76,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,87; 42,21</t>
+          <t>17,3; 41,74</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,22</t>
+          <t>7,09; 18,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,25</t>
+          <t>8,83; 20,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 21,58</t>
+          <t>9,42; 21,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 21,19</t>
+          <t>12,19; 21,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 27,85</t>
+          <t>16,67; 27,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 22,06</t>
+          <t>12,57; 22,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,22; 21,93</t>
+          <t>11,48; 22,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,69; 21,7</t>
+          <t>15,08; 21,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,51</t>
+          <t>14,56; 22,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,19; 19,96</t>
+          <t>11,98; 19,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,92; 20,04</t>
+          <t>11,69; 19,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,31</t>
+          <t>15,02; 20,27</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5455; 17316</t>
+          <t>6099; 18198</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8830; 24836</t>
+          <t>8551; 23810</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7731; 20393</t>
+          <t>8133; 21488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9112; 20191</t>
+          <t>9105; 20019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24417; 46745</t>
+          <t>24504; 46033</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26874; 50202</t>
+          <t>26697; 49830</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18536; 41315</t>
+          <t>18059; 40768</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34283; 51619</t>
+          <t>33695; 50983</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34147; 59141</t>
+          <t>33910; 58378</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38530; 67437</t>
+          <t>38240; 66898</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30275; 56352</t>
+          <t>31183; 56104</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46041; 66986</t>
+          <t>45992; 66061</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4715</t>
+          <t>0; 3576</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>984; 8892</t>
+          <t>1023; 9112</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1502; 8202</t>
+          <t>1542; 8348</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4238; 12107</t>
+          <t>3939; 11878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3984; 11441</t>
+          <t>4079; 11382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2298; 12017</t>
+          <t>2812; 11824</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3357; 15206</t>
+          <t>3970; 17340</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8850; 17556</t>
+          <t>8868; 18228</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4286; 14308</t>
+          <t>3768; 14398</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5228; 17525</t>
+          <t>4760; 17303</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7064; 20936</t>
+          <t>6607; 21436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14818; 26157</t>
+          <t>14155; 26401</t>
         </is>
       </c>
     </row>
@@ -1920,27 +1920,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>885; 7465</t>
+          <t>833; 6854</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>874; 2028</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1475; 7417</t>
+          <t>1737; 7406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3361; 9781</t>
+          <t>3925; 10592</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2225; 7027</t>
+          <t>2211; 7337</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6133; 16085</t>
+          <t>5970; 15553</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1050; 6452</t>
+          <t>1091; 6452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2178; 10013</t>
+          <t>1280; 9078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5200; 12286</t>
+          <t>5035; 12148</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9267; 23059</t>
+          <t>8978; 22788</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12129; 29601</t>
+          <t>12907; 30208</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11525; 26215</t>
+          <t>11444; 26023</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18534; 33016</t>
+          <t>18987; 33033</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38331; 64313</t>
+          <t>38499; 63705</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34297; 60967</t>
+          <t>34748; 61214</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30009; 58628</t>
+          <t>30705; 59190</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51208; 70827</t>
+          <t>49223; 69173</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51325; 80466</t>
+          <t>52046; 79541</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51497; 84352</t>
+          <t>50642; 83799</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46339; 77914</t>
+          <t>45469; 75345</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72393; 97898</t>
+          <t>72414; 97724</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$privada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 17,66</t>
+          <t>5,9; 17,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 19,18</t>
+          <t>7,37; 18,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,7; 22,99</t>
+          <t>8,3; 21,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,32; 20,5</t>
+          <t>9,91; 21,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,9; 22,36</t>
+          <t>12,2; 22,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 19,86</t>
+          <t>10,34; 19,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 19,55</t>
+          <t>8,86; 19,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,08; 19,79</t>
+          <t>13,54; 20,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 18,9</t>
+          <t>10,58; 18,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,2; 17,84</t>
+          <t>10,23; 17,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,32; 18,58</t>
+          <t>10,04; 18,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,94; 18,59</t>
+          <t>12,97; 18,92</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,2</t>
+          <t>0,0; 26,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 45,53</t>
+          <t>5,11; 39,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 36,49</t>
+          <t>6,96; 35,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 27,61</t>
+          <t>8,68; 26,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 84,32</t>
+          <t>30,9; 85,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,29; 55,9</t>
+          <t>11,12; 59,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 33,32</t>
+          <t>8,03; 32,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,22; 33,35</t>
+          <t>15,75; 32,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 52,0</t>
+          <t>16,42; 51,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,56; 42,03</t>
+          <t>11,62; 41,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,82; 28,61</t>
+          <t>9,26; 28,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,49; 27,03</t>
+          <t>14,56; 26,93</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>26,92%</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 73,19</t>
+          <t>8,75; 79,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,49; 48,98</t>
+          <t>10,56; 48,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,92; 91,53</t>
+          <t>33,91; 91,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 52,46</t>
+          <t>14,29; 49,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,52; 74,28</t>
+          <t>28,87; 75,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,91; 100,0</t>
+          <t>16,65; 100,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 76,41</t>
+          <t>17,47; 79,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 41,74</t>
+          <t>15,34; 41,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,0</t>
+          <t>7,1; 17,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 20,67</t>
+          <t>8,83; 20,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,43</t>
+          <t>9,13; 21,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,19; 21,2</t>
+          <t>11,75; 21,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,59</t>
+          <t>16,56; 27,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 22,15</t>
+          <t>12,51; 22,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 22,14</t>
+          <t>11,5; 21,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,08; 21,2</t>
+          <t>15,39; 21,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,25</t>
+          <t>14,77; 22,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,98; 19,83</t>
+          <t>12,3; 19,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,38</t>
+          <t>11,91; 19,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 20,27</t>
+          <t>14,86; 20,02</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41940</t>
+          <t>45792</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55910</t>
+          <t>61024</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6099; 18198</t>
+          <t>6074; 18034</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8551; 23810</t>
+          <t>9152; 23300</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8133; 21488</t>
+          <t>7759; 20491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9105; 20019</t>
+          <t>10283; 22440</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24504; 46033</t>
+          <t>25115; 46515</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26697; 49830</t>
+          <t>25929; 50042</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18059; 40768</t>
+          <t>18476; 41039</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33695; 50983</t>
+          <t>37481; 55880</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33910; 58378</t>
+          <t>32678; 58268</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38240; 66898</t>
+          <t>38362; 67259</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31183; 56104</t>
+          <t>30337; 55574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>45992; 66061</t>
+          <t>49345; 72015</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20306</t>
+          <t>22152</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3576</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1023; 9112</t>
+          <t>1023; 8000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1542; 8348</t>
+          <t>1591; 8224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3939; 11878</t>
+          <t>4106; 12419</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4079; 11382</t>
+          <t>4172; 11502</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2812; 11824</t>
+          <t>2353; 12561</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3970; 17340</t>
+          <t>4176; 17007</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8868; 18228</t>
+          <t>9870; 20423</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3768; 14398</t>
+          <t>4546; 14210</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4760; 17303</t>
+          <t>4782; 17225</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6607; 21436</t>
+          <t>6939; 21516</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14155; 26401</t>
+          <t>16008; 29618</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8700</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>833; 6854</t>
+          <t>820; 7410</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1737; 7406</t>
+          <t>1749; 8058</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3925; 10592</t>
+          <t>3925; 10618</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1955,27 +1955,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2211; 7337</t>
+          <t>2250; 7754</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5970; 15553</t>
+          <t>6044; 15713</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1091; 6452</t>
+          <t>1074; 6452</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1280; 9078</t>
+          <t>2075; 9446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5035; 12148</t>
+          <t>4957; 13421</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>59247</t>
+          <t>64884</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>91876</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8978; 22788</t>
+          <t>8993; 22591</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12907; 30208</t>
+          <t>12905; 30593</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11444; 26023</t>
+          <t>11091; 25643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18987; 33033</t>
+          <t>19707; 35758</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>38499; 63705</t>
+          <t>38243; 63953</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34748; 61214</t>
+          <t>34573; 60808</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30705; 59190</t>
+          <t>30741; 57077</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49223; 69173</t>
+          <t>54650; 76700</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52046; 79541</t>
+          <t>52795; 80466</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50642; 83799</t>
+          <t>51976; 82817</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45469; 75345</t>
+          <t>46327; 76812</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72414; 97724</t>
+          <t>77687; 104686</t>
         </is>
       </c>
     </row>
